--- a/test/fixtures/parity/formula_results.xlsx
+++ b/test/fixtures/parity/formula_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Kind</t>
   </si>
@@ -34,13 +34,16 @@
     <t>No result</t>
   </si>
   <si>
-    <t>first</t>
+    <t>plain</t>
   </si>
   <si>
     <t>shared</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>plain false</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="4" max="4" width="9" style="1" customWidth="1"/>
@@ -459,19 +462,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="e">
-        <f>1/0</f>
+        <f t="shared" ref="C2:C3" si="1">1/0</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D3" si="1">DATE(2026,10,18)</f>
+        <f t="shared" ref="D2:D3" si="2">DATE(2026,10,18)</f>
         <v>46313</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E3" si="2">1+1</f>
+        <f t="shared" ref="E2:E3" si="3">1+1</f>
         <v>2</v>
       </c>
       <c r="F2" t="str">
-        <f t="shared" ref="F2:F3" si="3">"a"&amp;"b"</f>
+        <f t="shared" ref="F2:F3" si="4">"a"&amp;"b"</f>
         <v>ab</v>
       </c>
       <c r="G2">
@@ -484,25 +487,53 @@
       </c>
       <c r="B3" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" si="2"/>
+        <v>36525.5</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="3"/>
+        <v>3.25</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="4"/>
+        <v>cd</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="C4" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="D3" s="1">
-        <f t="shared" si="1"/>
-        <v>36525.5</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" si="3"/>
-        <v>cd</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D4" s="1">
+        <f>D2+1</f>
+        <v>46314</v>
+      </c>
+      <c r="E4">
+        <f>0*1</f>
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G4" t="s">
         <v>9</v>
       </c>
     </row>
